--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486354_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486354_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8272</v>
+        <v>3.6078</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4627</v>
+        <v>4.5515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3645</v>
+        <v>-0.9437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6195000000000001</v>
+        <v>4.5067</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2466</v>
+        <v>2.7768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3729</v>
+        <v>1.7299</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0003</v>
+        <v>4.6353</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1151</v>
+        <v>3.9085</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1147</v>
+        <v>0.7267</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6198</v>
+        <v>-0.1285</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3617</v>
+        <v>-1.1318</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2582</v>
+        <v>1.0032</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.9576</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>3.84</v>
+        <v>-0.8989</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5304</v>
+        <v>-0.1262</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6904</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0901</v>
+        <v>0.989</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7872</v>
+        <v>0.4705</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6971000000000001</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5067</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7768</v>
+        <v>0.2466</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7299</v>
+        <v>0.3729</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6353</v>
+        <v>-0.0003</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9085</v>
+        <v>-0.1151</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7267</v>
+        <v>0.1147</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1285</v>
+        <v>0.6198</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1318</v>
+        <v>0.3617</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0032</v>
+        <v>0.2582</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4166</v>
+        <v>1.0019</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8904</v>
+        <v>1.5382</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5261</v>
+        <v>-0.5363</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1116</v>
+        <v>-0.5464</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3704</v>
+        <v>-0.4898</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7412</v>
+        <v>-0.0565</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3353</v>
+        <v>-1.4409</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7481</v>
+        <v>-2.4481</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4128</v>
+        <v>1.0072</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1091</v>
+        <v>-1.1634</v>
       </c>
       <c r="K5" t="n">
-        <v>0.949</v>
+        <v>-1.3164</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8399</v>
+        <v>0.153</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2262</v>
+        <v>-0.2776</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2009</v>
+        <v>-1.1318</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4271</v>
+        <v>0.8542</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9694</v>
+        <v>0.1121</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4795</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4899</v>
+        <v>0.0459</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X5" t="n">
         <v>-1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1998</v>
+        <v>-0.7271</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2974</v>
+        <v>-0.0784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4409</v>
+        <v>0.3353</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4481</v>
+        <v>0.7481</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0072</v>
+        <v>-0.4128</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1634</v>
+        <v>0.1091</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3164</v>
+        <v>0.949</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>-0.8399</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2776</v>
+        <v>0.2262</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1318</v>
+        <v>-0.2009</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8542</v>
+        <v>0.4271</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5414</v>
+        <v>-0.5849</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.1875</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2001</v>
+        <v>-0.3975</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2966</v>
+        <v>-1.8327</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.226</v>
+        <v>-3.3407</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0705</v>
+        <v>1.5081</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1269</v>
+        <v>0.3814</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3802</v>
+        <v>-0.1644</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7467</v>
+        <v>0.5458</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3236</v>
+        <v>-0.4384</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3618</v>
+        <v>-0.3436</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>-0.0948</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8033</v>
+        <v>0.8198</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0184</v>
+        <v>0.1792</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7849</v>
+        <v>0.6407</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>-4.5676</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2365</v>
+        <v>-0.0592</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.3401</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5516</v>
+        <v>-0.3993</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5857</v>
+        <v>1.3252</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.671</v>
+        <v>-1.8928</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.1483</v>
+        <v>-0.8223</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4773</v>
+        <v>-1.0705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3814</v>
+        <v>-1.1269</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1644</v>
+        <v>-0.3802</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5458</v>
+        <v>-0.7467</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4384</v>
+        <v>-0.3236</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3436</v>
+        <v>-0.3618</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0948</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8198</v>
+        <v>-0.8033</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1792</v>
+        <v>-0.0184</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6407</v>
+        <v>-0.7849</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.4801</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.5676</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8976</v>
+        <v>-0.8328</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>-0.2812</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4301</v>
+        <v>-0.5516</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3252</v>
+        <v>-0.5857</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5273</v>
+        <v>-2.9727</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4749</v>
+        <v>-2.9543</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0524</v>
+        <v>-0.0184</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8075</v>
+        <v>-1.9819</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9828</v>
+        <v>-0.7333</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1754</v>
+        <v>-1.2487</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5977</v>
+        <v>-0.5593</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5531</v>
+        <v>0.1825</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1507</v>
+        <v>-0.7418</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4051</v>
+        <v>-1.4226</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4298</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0247</v>
+        <v>-0.5068</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0875</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6323</v>
+        <v>-0.1208</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0274</v>
+        <v>-0.0024</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6048</v>
+        <v>-0.1184</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9652</v>
+        <v>-3.216</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7618</v>
+        <v>-1.0711</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2034</v>
+        <v>-2.1448</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9819</v>
+        <v>-0.8075</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7333</v>
+        <v>-1.9828</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2487</v>
+        <v>1.1754</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5593</v>
+        <v>0.5977</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1825</v>
+        <v>-0.5531</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7418</v>
+        <v>1.1507</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4226</v>
+        <v>-1.4051</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.4298</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5068</v>
+        <v>0.0247</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1133</v>
+        <v>-1.321</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8099</v>
+        <v>-0.6237</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3033</v>
+        <v>-0.6973</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3404</v>
+        <v>-5.5764</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0963</v>
+        <v>-4.3631</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2442</v>
+        <v>-1.2133</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1859</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4145</v>
+        <v>-0.6504</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0036</v>
+        <v>-0.2632</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4181</v>
+        <v>-0.3873</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.6475</v>
+        <v>-12.6202</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.1018</v>
+        <v>-9.074300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5457</v>
+        <v>-3.545500000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0243</v>
+        <v>-1.024299999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-2.7373</v>
@@ -1369,13 +1369,13 @@
         <v>3.1807</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1234999999999998</v>
+        <v>-0.1235</v>
       </c>
       <c r="M12" t="n">
         <v>-4.0817</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.918299999999999</v>
+        <v>-5.9183</v>
       </c>
       <c r="O12" t="n">
         <v>1.8366</v>
@@ -1390,13 +1390,13 @@
         <v>10.8751</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.530600000000001</v>
+        <v>-3.503</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4265000000000005</v>
+        <v>0.6008</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1038</v>
+        <v>-4.1041</v>
       </c>
       <c r="V12" t="n">
         <v>1.6949</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8303</v>
+        <v>6.3955</v>
       </c>
       <c r="E13" t="n">
-        <v>4.021</v>
+        <v>4.468</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8093</v>
+        <v>1.9275</v>
       </c>
       <c r="G13" t="n">
         <v>3.1722</v>
@@ -1468,13 +1468,13 @@
         <v>3.0451</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3871</v>
+        <v>0.1782</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5564</v>
+        <v>-0.1093</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1693</v>
+        <v>0.2875</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8437</v>
+        <v>4.6189</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2767</v>
+        <v>3.2446</v>
       </c>
       <c r="F14" t="n">
-        <v>2.567</v>
+        <v>1.3743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3604</v>
+        <v>1.6814</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9078</v>
+        <v>2.938</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5474</v>
+        <v>-1.2566</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7716</v>
+        <v>2.4361</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3637</v>
+        <v>3.5039</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5921</v>
+        <v>-1.0678</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5888</v>
+        <v>-0.7548</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5442</v>
+        <v>-0.5659</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0446</v>
+        <v>-0.1889</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0451</v>
+        <v>3.2626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.721</v>
+        <v>0.3503</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4627</v>
+        <v>0.1586</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2584</v>
+        <v>0.1917</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1952</v>
+        <v>1.4997</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>2.8249</v>
       </c>
       <c r="X14" t="n">
         <v>-1.3252</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6006</v>
+        <v>4.3492</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1192</v>
+        <v>1.9414</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5185999999999999</v>
+        <v>2.4078</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2189</v>
+        <v>2.3604</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5472</v>
+        <v>2.9078</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3283</v>
+        <v>-0.5474</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5654</v>
+        <v>1.7716</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4507</v>
+        <v>2.3637</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1147</v>
+        <v>-0.5921</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7843</v>
+        <v>0.5888</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9978</v>
+        <v>0.5442</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2136</v>
+        <v>0.0446</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>3.0451</v>
       </c>
       <c r="S15" t="n">
-        <v>5.1245</v>
+        <v>0.2265</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5989</v>
+        <v>0.1274</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5256</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W15" t="n">
         <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4397</v>
+        <v>1.5253</v>
       </c>
       <c r="E16" t="n">
-        <v>2.127</v>
+        <v>-2.2629</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3127</v>
+        <v>3.7882</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6814</v>
+        <v>-0.2953</v>
       </c>
       <c r="H16" t="n">
-        <v>2.938</v>
+        <v>-0.1885</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2566</v>
+        <v>-0.1068</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4361</v>
+        <v>-1.167</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5039</v>
+        <v>-1.0156</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0678</v>
+        <v>-0.1514</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7548</v>
+        <v>0.8717</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5659</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1889</v>
+        <v>0.0446</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2626</v>
+        <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8289</v>
+        <v>0.298</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9589</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.13</v>
+        <v>0.3064</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4997</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2787</v>
+        <v>1.2317</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2629</v>
+        <v>-1.7986</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5416</v>
+        <v>3.0302</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2953</v>
+        <v>-2.415</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1885</v>
+        <v>-3.035</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1068</v>
+        <v>0.62</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.167</v>
+        <v>-1.7272</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0156</v>
+        <v>-2.6851</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1514</v>
+        <v>0.9578</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8717</v>
+        <v>-0.6878</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.3499</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0446</v>
+        <v>-0.3379</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>3.4801</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6101</v>
+        <v>3.4801</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0514</v>
+        <v>0.9061</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.6682</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0598</v>
+        <v>0.2379</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2317</v>
+        <v>0.8521</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7986</v>
+        <v>0.5292</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0302</v>
+        <v>0.3229</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.415</v>
+        <v>1.1612</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.035</v>
+        <v>1.0585</v>
       </c>
       <c r="I18" t="n">
-        <v>0.62</v>
+        <v>0.1028</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7272</v>
+        <v>1.4617</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.6851</v>
+        <v>1.4234</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9578</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6878</v>
+        <v>-0.3004</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3499</v>
+        <v>-0.365</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3379</v>
+        <v>0.0645</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4801</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>3.4801</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9061</v>
+        <v>0.3434</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6682</v>
+        <v>0.155</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2379</v>
+        <v>0.1884</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7211</v>
+        <v>0.51</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3057</v>
+        <v>1.2135</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4154</v>
+        <v>-0.7036</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1612</v>
+        <v>-0.2189</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0585</v>
+        <v>-0.5472</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1028</v>
+        <v>0.3283</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4617</v>
+        <v>0.5654</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4234</v>
+        <v>0.4507</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3004</v>
+        <v>-0.7843</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.365</v>
+        <v>-0.9978</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0645</v>
+        <v>0.2136</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2123</v>
+        <v>2.0339</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>1.6932</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2808</v>
+        <v>0.3407</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0765</v>
+        <v>-0.3641</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7651</v>
+        <v>-1.3239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8416</v>
+        <v>0.9598</v>
       </c>
       <c r="G20" t="n">
         <v>-1.095</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1715</v>
+        <v>0.7309</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3447</v>
+        <v>0.7859</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1732</v>
+        <v>-0.055</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7559</v>
+        <v>-1.0172</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3319</v>
+        <v>0.8907</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0877</v>
+        <v>-1.9079</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7954</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.483</v>
+        <v>0.2557</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.5504</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4746</v>
+        <v>-0.2947</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1043</v>
+        <v>-1.6765</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0231</v>
+        <v>-0.6878</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0812</v>
+        <v>-0.9888</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2927</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4419</v>
+        <v>-0.0141</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2055</v>
+        <v>0.1298</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9347</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5146</v>
+        <v>-2.0322</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.786</v>
+        <v>-2.6684</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2714</v>
+        <v>0.6362</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2387</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5157</v>
+        <v>-0.0333</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1644</v>
+        <v>-0.0469</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3513</v>
+        <v>0.0135</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.6475</v>
+        <v>14.3927</v>
       </c>
       <c r="E24" t="n">
         <v>3.545799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1017</v>
+        <v>10.8466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.024200000000001</v>
+        <v>1.024199999999999</v>
       </c>
       <c r="H24" t="n">
         <v>2.737400000000001</v>
@@ -2299,7 +2299,7 @@
         <v>-1.7131</v>
       </c>
       <c r="J24" t="n">
-        <v>4.081700000000001</v>
+        <v>4.081699999999999</v>
       </c>
       <c r="K24" t="n">
         <v>5.918200000000001</v>
@@ -2326,19 +2326,19 @@
         <v>20.663</v>
       </c>
       <c r="S24" t="n">
-        <v>4.530200000000001</v>
+        <v>5.275600000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>4.104000000000001</v>
+        <v>4.1039</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4262999999999998</v>
+        <v>1.1716</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6949</v>
       </c>
       <c r="W24" t="n">
-        <v>6.2356</v>
+        <v>6.235599999999998</v>
       </c>
       <c r="X24" t="n">
         <v>-7.930599999999999</v>
